--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_37.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2388899.266419165</v>
+        <v>2389970.39013144</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984941063</v>
+        <v>657188.6984941058</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984941063</v>
+        <v>657188.6984941058</v>
       </c>
     </row>
     <row r="11">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557292</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -666,10 +666,10 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>6.688316575839963</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.347322035758776</v>
       </c>
       <c r="H2" t="n">
         <v>3.81023156784903</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.798687867827562</v>
       </c>
       <c r="S2" t="n">
         <v>85.50414770182039</v>
@@ -736,13 +736,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>138.8829806321346</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -793,10 +793,10 @@
         <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W3" t="n">
-        <v>164.3799542291337</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>133.6519859716246</v>
@@ -1033,13 +1033,13 @@
         <v>374</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>133.6173909563443</v>
+        <v>334.4909338603293</v>
       </c>
     </row>
     <row r="7">
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716245</v>
+        <v>161.4306305222035</v>
       </c>
       <c r="S9" t="n">
         <v>62.48881128536601</v>
@@ -1264,16 +1264,16 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>374</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>340.0389319121197</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1447,7 +1447,7 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>265.042185205795</v>
       </c>
       <c r="D12" t="n">
         <v>28.93768689770263</v>
@@ -1459,10 +1459,10 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H12" t="n">
-        <v>5.544181526043773</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>402.2042587319003</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S12" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T12" t="n">
-        <v>402.1759444627968</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U12" t="n">
         <v>81.1584257979226</v>
@@ -1510,7 +1510,7 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y12" t="n">
         <v>80.39139276613435</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.305168319657323</v>
+        <v>3.305168319656873</v>
       </c>
       <c r="M13" t="n">
         <v>97.89093927140236</v>
@@ -1687,22 +1687,22 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>246.6143699821881</v>
+        <v>56.66675767574558</v>
       </c>
       <c r="F15" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>5.950139648612264</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H15" t="n">
         <v>5.544181526043758</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1741,13 +1741,13 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y15" t="n">
         <v>80.39139276613435</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3.305168319657548</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M16" t="n">
         <v>97.89093927140237</v>
@@ -1799,7 +1799,7 @@
         <v>150.9111244520127</v>
       </c>
       <c r="O16" t="n">
-        <v>227.9026788331133</v>
+        <v>225.052317355647</v>
       </c>
       <c r="P16" t="n">
         <v>288.4057989676218</v>
@@ -1857,7 +1857,7 @@
         <v>82.58591040609919</v>
       </c>
       <c r="H17" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>265.042185205795</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -1933,10 +1933,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H18" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,16 +1966,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>179.2619859716246</v>
+        <v>402.2042587319003</v>
       </c>
       <c r="S18" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T18" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U18" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V18" t="n">
         <v>95.51066719152016</v>
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M19" t="n">
-        <v>95.04057779393561</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N19" t="n">
         <v>150.9111244520127</v>
@@ -2045,10 +2045,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S19" t="n">
-        <v>31.84005347334724</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>82.58591040609919</v>
       </c>
       <c r="H20" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2158,22 +2158,22 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D21" t="n">
         <v>28.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H21" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,25 +2203,25 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S21" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T21" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U21" t="n">
-        <v>81.15842579792258</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V21" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>303.3336655264099</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M22" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N22" t="n">
         <v>150.9111244520127</v>
@@ -2282,10 +2282,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S22" t="n">
-        <v>28.98969199588095</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>83.28199540259408</v>
       </c>
       <c r="H23" t="n">
-        <v>73.89995518593946</v>
+        <v>73.2038701894446</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T23" t="n">
         <v>261.2171194170061</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>216.185300165179</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>265.0421852057948</v>
       </c>
       <c r="D24" t="n">
         <v>28.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G24" t="n">
         <v>5.950139648612264</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>179.2619859716245</v>
@@ -2452,13 +2452,13 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V24" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y24" t="n">
         <v>80.39139276613435</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>6.155529797123449</v>
+        <v>3.305168319657098</v>
       </c>
       <c r="M25" t="n">
         <v>97.89093927140237</v>
@@ -2522,7 +2522,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>28.98969199588095</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H26" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>273.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>191.6213476863115</v>
+        <v>192.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2632,22 +2632,22 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>251.8799596579784</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H27" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S27" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T27" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U27" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V27" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517959</v>
       </c>
       <c r="W27" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>100.8627394453875</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M28" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N28" t="n">
         <v>150.9111244520127</v>
@@ -2753,13 +2753,13 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q28" t="n">
-        <v>351.422266425598</v>
+        <v>348.5719049481316</v>
       </c>
       <c r="R28" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S28" t="n">
-        <v>28.98969199588089</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H29" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U29" t="n">
-        <v>329.4071814013618</v>
+        <v>330.1032663978569</v>
       </c>
       <c r="V29" t="n">
         <v>310.8510241668239</v>
@@ -2872,19 +2872,19 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>251.8799596579782</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>20.63624233787687</v>
+        <v>243.5785150981523</v>
       </c>
       <c r="G30" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H30" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,28 +2914,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S30" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U30" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V30" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3.305168319656873</v>
+        <v>3.305168319657098</v>
       </c>
       <c r="M31" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N31" t="n">
         <v>150.9111244520127</v>
@@ -2993,10 +2993,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S31" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3039,10 +3039,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H32" t="n">
-        <v>73.89995518593946</v>
+        <v>73.20387018944457</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T32" t="n">
         <v>261.2171194170061</v>
@@ -3118,13 +3118,13 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H33" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I33" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,25 +3148,25 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R33" t="n">
-        <v>179.2619859716245</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S33" t="n">
-        <v>132.901311285366</v>
+        <v>283.5300548042184</v>
       </c>
       <c r="T33" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1584257979226</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V33" t="n">
-        <v>128.5053276453529</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>419.8627394453875</v>
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3.305168319657098</v>
+        <v>3.305168319656873</v>
       </c>
       <c r="M34" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N34" t="n">
         <v>150.9111244520127</v>
@@ -3230,10 +3230,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S34" t="n">
-        <v>31.84005347334727</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>60.92708723799848</v>
+        <v>64.22801704855405</v>
       </c>
       <c r="T35" t="n">
         <v>183.2171194170061</v>
       </c>
       <c r="U35" t="n">
-        <v>252.1032663978569</v>
+        <v>248.8023365873013</v>
       </c>
       <c r="V35" t="n">
         <v>232.8510241668239</v>
@@ -3346,13 +3346,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R36" t="n">
-        <v>101.2619859716246</v>
+        <v>374</v>
       </c>
       <c r="S36" t="n">
-        <v>310.8139757873043</v>
+        <v>54.90131128536602</v>
       </c>
       <c r="T36" t="n">
         <v>5.175944462796835</v>
@@ -3403,7 +3403,7 @@
         <v>17.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>35.37314290982852</v>
+        <v>369.5213351651297</v>
       </c>
       <c r="X36" t="n">
         <v>22.86273944538755</v>
@@ -3507,13 +3507,13 @@
         <v>13.33915573984979</v>
       </c>
       <c r="E38" t="n">
-        <v>4.06235979631303</v>
+        <v>7.363289606868648</v>
       </c>
       <c r="F38" t="n">
         <v>7.889628708011855</v>
       </c>
       <c r="G38" t="n">
-        <v>5.2819954025941</v>
+        <v>5.281995402594077</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>64.22801704855405</v>
+        <v>64.22801704855408</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
       </c>
       <c r="U38" t="n">
-        <v>252.1032663978569</v>
+        <v>248.8023365873013</v>
       </c>
       <c r="V38" t="n">
         <v>232.8510241668239</v>
@@ -3577,25 +3577,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H39" t="n">
-        <v>71.86027680838114</v>
+        <v>184.1066809851165</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3622,25 +3622,25 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>101.2619859716246</v>
+        <v>101.2619859716245</v>
       </c>
       <c r="S39" t="n">
-        <v>54.90131128536602</v>
+        <v>54.90131128536603</v>
       </c>
       <c r="T39" t="n">
-        <v>5.175944462796835</v>
+        <v>5.175944462796849</v>
       </c>
       <c r="U39" t="n">
-        <v>3.158425797922597</v>
+        <v>3.158425797922575</v>
       </c>
       <c r="V39" t="n">
         <v>17.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>35.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X39" t="n">
         <v>22.86273944538755</v>
@@ -3689,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>19.89093927140236</v>
+        <v>19.89093927140237</v>
       </c>
       <c r="N40" t="n">
-        <v>72.91112445201273</v>
+        <v>72.9111244520127</v>
       </c>
       <c r="O40" t="n">
         <v>149.9026788331133</v>
@@ -3704,7 +3704,7 @@
         <v>273.422266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>299.845046013938</v>
+        <v>299.8450460139379</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,22 +3735,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>22.79257314441494</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3789,22 +3789,22 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>113.8095999937037</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>336.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3829,10 +3829,10 @@
         <v>46.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>31.95013964861226</v>
+        <v>31.95013964861225</v>
       </c>
       <c r="H42" t="n">
-        <v>31.54418152604376</v>
+        <v>31.54418152604377</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,10 +3859,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.386773445425144</v>
       </c>
       <c r="R42" t="n">
-        <v>207.6487594170497</v>
+        <v>205.2619859716246</v>
       </c>
       <c r="S42" t="n">
         <v>158.901311285366</v>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3938,13 +3938,13 @@
         <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>374</v>
+        <v>371.7620052112061</v>
       </c>
       <c r="R43" t="n">
-        <v>121.6529444826084</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334727</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,22 +3972,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>156.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>38.29942252857128</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>79.52595155467309</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4023,22 +4023,22 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>218.3174326828064</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>32.15552979712344</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         <v>176.9111244520127</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>253.9026788331133</v>
       </c>
       <c r="P46" t="n">
         <v>314.4057989676218</v>
@@ -4178,10 +4178,10 @@
         <v>374</v>
       </c>
       <c r="R46" t="n">
-        <v>166.4889690665855</v>
+        <v>2.581873503942786</v>
       </c>
       <c r="S46" t="n">
-        <v>57.84005347334724</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.7310038072336</v>
+        <v>106.9141473750828</v>
       </c>
       <c r="C2" t="n">
-        <v>58.756682349664</v>
+        <v>56.93982591751323</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069325007</v>
+        <v>46.4962342610993</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398882</v>
+        <v>42.08887102183805</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>37.14985212485637</v>
       </c>
       <c r="G2" t="n">
         <v>33.76871875540306</v>
@@ -4321,52 +4321,52 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>145.6202453266332</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M2" t="n">
-        <v>145.6202453266332</v>
+        <v>755.48</v>
       </c>
       <c r="N2" t="n">
-        <v>515.8802453266331</v>
+        <v>755.48</v>
       </c>
       <c r="O2" t="n">
-        <v>886.1402453266331</v>
+        <v>1125.74</v>
       </c>
       <c r="P2" t="n">
-        <v>1256.400245326633</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.183143567851</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606416</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178447</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698507</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861902</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165461</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138515</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190975</v>
       </c>
     </row>
     <row r="3">
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1092.400476380049</v>
+        <v>862.620151643509</v>
       </c>
       <c r="C3" t="n">
-        <v>727.6530900714438</v>
+        <v>862.620151643509</v>
       </c>
       <c r="D3" t="n">
-        <v>376.2008810838653</v>
+        <v>722.3343126211507</v>
       </c>
       <c r="E3" t="n">
         <v>376.2008810838653</v>
@@ -4436,16 +4436,16 @@
         <v>1293.161446951808</v>
       </c>
       <c r="V3" t="n">
-        <v>1278.504207364414</v>
+        <v>915.3836691740303</v>
       </c>
       <c r="W3" t="n">
-        <v>1112.463849557208</v>
+        <v>882.6835248206681</v>
       </c>
       <c r="X3" t="n">
-        <v>1092.400476380049</v>
+        <v>862.620151643509</v>
       </c>
       <c r="Y3" t="n">
-        <v>1092.400476380049</v>
+        <v>862.620151643509</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>797.7579367596561</v>
+        <v>815.2534162650522</v>
       </c>
       <c r="C4" t="n">
-        <v>797.7579367596561</v>
+        <v>941.255422083488</v>
       </c>
       <c r="D4" t="n">
-        <v>911.0770808846562</v>
+        <v>1054.574566208488</v>
       </c>
       <c r="E4" t="n">
-        <v>1028.905985096069</v>
+        <v>1172.403470419901</v>
       </c>
       <c r="F4" t="n">
-        <v>1153.266957688005</v>
+        <v>1296.764443011836</v>
       </c>
       <c r="G4" t="n">
-        <v>1153.266957688005</v>
+        <v>1296.764443011836</v>
       </c>
       <c r="H4" t="n">
-        <v>1153.266957688005</v>
+        <v>1296.764443011836</v>
       </c>
       <c r="I4" t="n">
-        <v>1153.266957688005</v>
+        <v>1296.764443011836</v>
       </c>
       <c r="J4" t="n">
-        <v>1364.479428358214</v>
+        <v>1296.764443011836</v>
       </c>
       <c r="K4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.273682802524</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1258.790761928658</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.177358901337</v>
+        <v>932.9209073660642</v>
       </c>
       <c r="P4" t="n">
-        <v>774.2966876474056</v>
+        <v>665.0402361121327</v>
       </c>
       <c r="Q4" t="n">
-        <v>460.7236912579127</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>139.176451535273</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>328.0301733170287</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U4" t="n">
-        <v>574.5912984143317</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="V4" t="n">
-        <v>574.5912984143317</v>
+        <v>269.1650686358568</v>
       </c>
       <c r="W4" t="n">
-        <v>574.5912984143317</v>
+        <v>441.0559868955343</v>
       </c>
       <c r="X4" t="n">
-        <v>574.5912984143317</v>
+        <v>592.0867779197278</v>
       </c>
       <c r="Y4" t="n">
-        <v>686.000599093364</v>
+        <v>703.4960785987601</v>
       </c>
     </row>
     <row r="5">
@@ -4558,25 +4558,25 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>327.128108133742</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>697.388108133742</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>724.4391204399794</v>
+        <v>29.92</v>
       </c>
       <c r="C6" t="n">
-        <v>724.4391204399794</v>
+        <v>29.92</v>
       </c>
       <c r="D6" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>1294.664012937232</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>1290.14538216673</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U6" t="n">
-        <v>1289.947477320344</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V6" t="n">
-        <v>912.1696995425657</v>
+        <v>765.6307811168858</v>
       </c>
       <c r="W6" t="n">
-        <v>879.4695551892036</v>
+        <v>387.853003339108</v>
       </c>
       <c r="X6" t="n">
-        <v>859.4061820120444</v>
+        <v>367.7896301619489</v>
       </c>
       <c r="Y6" t="n">
-        <v>724.4391204399794</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>182.101013416203</v>
+        <v>1021.390865612444</v>
       </c>
       <c r="C7" t="n">
-        <v>308.1030192346387</v>
+        <v>1147.39287143088</v>
       </c>
       <c r="D7" t="n">
-        <v>421.4221633596388</v>
+        <v>1260.71201555588</v>
       </c>
       <c r="E7" t="n">
-        <v>539.2510675710519</v>
+        <v>1378.540919767293</v>
       </c>
       <c r="F7" t="n">
-        <v>663.6120401629873</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="G7" t="n">
-        <v>817.2007011318399</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H7" t="n">
-        <v>988.3362771109096</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I7" t="n">
-        <v>1214.945251784697</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>70.34367574991083</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>70.34367574991083</v>
+        <v>276.481125097303</v>
       </c>
       <c r="V7" t="n">
-        <v>70.34367574991083</v>
+        <v>475.302517983249</v>
       </c>
       <c r="W7" t="n">
-        <v>70.34367574991083</v>
+        <v>647.1934362429264</v>
       </c>
       <c r="X7" t="n">
-        <v>70.34367574991083</v>
+        <v>798.2242272671199</v>
       </c>
       <c r="Y7" t="n">
-        <v>70.34367574991083</v>
+        <v>909.6335279461522</v>
       </c>
     </row>
     <row r="8">
@@ -4798,22 +4798,22 @@
         <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>770.4399999999999</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>834.5019149748742</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M8" t="n">
-        <v>1067.648108133742</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1314.492137192891</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>1047.928564856972</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>1047.928564856972</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>1047.928564856972</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>701.7951333196861</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4898,28 +4898,28 @@
         <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1183.185868991135</v>
       </c>
       <c r="S9" t="n">
-        <v>1148.125094511552</v>
+        <v>1120.065857591776</v>
       </c>
       <c r="T9" t="n">
-        <v>1143.60646374105</v>
+        <v>1115.547226821274</v>
       </c>
       <c r="U9" t="n">
-        <v>765.8286859632726</v>
+        <v>1115.349321974887</v>
       </c>
       <c r="V9" t="n">
-        <v>751.1714463758785</v>
+        <v>1100.692082387493</v>
       </c>
       <c r="W9" t="n">
-        <v>373.3936685981007</v>
+        <v>1067.991938034131</v>
       </c>
       <c r="X9" t="n">
-        <v>29.92</v>
+        <v>1047.928564856972</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.92</v>
+        <v>1047.928564856972</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1210.2445873942</v>
+        <v>222.3787384544462</v>
       </c>
       <c r="C10" t="n">
-        <v>1336.246593212636</v>
+        <v>348.380744272882</v>
       </c>
       <c r="D10" t="n">
-        <v>1386.743548464727</v>
+        <v>461.6998883978821</v>
       </c>
       <c r="E10" t="n">
-        <v>1386.743548464727</v>
+        <v>579.5287926092951</v>
       </c>
       <c r="F10" t="n">
-        <v>1386.743548464727</v>
+        <v>703.8897652012306</v>
       </c>
       <c r="G10" t="n">
-        <v>1386.743548464727</v>
+        <v>857.4784261700831</v>
       </c>
       <c r="H10" t="n">
-        <v>1386.743548464727</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="I10" t="n">
-        <v>1386.743548464727</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K10" t="n">
         <v>1386.743548464727</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7737217817557</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U10" t="n">
-        <v>465.3348468790587</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="V10" t="n">
-        <v>664.1562397650047</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="W10" t="n">
-        <v>836.0471580246821</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="X10" t="n">
-        <v>987.0779490488756</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="Y10" t="n">
-        <v>1098.487249727908</v>
+        <v>110.6214007881541</v>
       </c>
     </row>
     <row r="11">
@@ -5032,16 +5032,16 @@
         <v>52.4</v>
       </c>
       <c r="J11" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K11" t="n">
-        <v>327.4727226113304</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L11" t="n">
-        <v>936.7915875547988</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M11" t="n">
-        <v>1585.241587554803</v>
+        <v>1632.421694143183</v>
       </c>
       <c r="N11" t="n">
         <v>2233.691587554807</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>502.743697048149</v>
+        <v>1050.160134179741</v>
       </c>
       <c r="C12" t="n">
-        <v>137.9963107395436</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D12" t="n">
-        <v>108.7663239741874</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E12" t="n">
-        <v>84.85511465912413</v>
+        <v>729.2995591035686</v>
       </c>
       <c r="F12" t="n">
-        <v>64.01042542894548</v>
+        <v>708.45486987339</v>
       </c>
       <c r="G12" t="n">
-        <v>58.00018335964018</v>
+        <v>380.2224055818624</v>
       </c>
       <c r="H12" t="n">
         <v>52.4</v>
@@ -5135,28 +5135,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1907.723677356515</v>
+        <v>1810.695670043663</v>
       </c>
       <c r="S12" t="n">
-        <v>1773.479928583418</v>
+        <v>1676.451921270566</v>
       </c>
       <c r="T12" t="n">
-        <v>1367.241600843219</v>
+        <v>1592.435815752589</v>
       </c>
       <c r="U12" t="n">
-        <v>1285.26339296653</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V12" t="n">
-        <v>1188.787971560954</v>
+        <v>1413.982186470324</v>
       </c>
       <c r="W12" t="n">
-        <v>1074.26964538941</v>
+        <v>1299.46386029878</v>
       </c>
       <c r="X12" t="n">
-        <v>650.1658681718469</v>
+        <v>1197.582305303438</v>
       </c>
       <c r="Y12" t="n">
-        <v>568.9624411353476</v>
+        <v>1116.378878266939</v>
       </c>
     </row>
     <row r="13">
@@ -5166,31 +5166,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C13" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D13" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E13" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F13" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G13" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H13" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I13" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J13" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K13" t="n">
         <v>1597.372803794637</v>
@@ -5229,13 +5229,13 @@
         <v>448.1134299289391</v>
       </c>
       <c r="W13" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X13" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y13" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="14">
@@ -5269,16 +5269,16 @@
         <v>52.4</v>
       </c>
       <c r="J14" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K14" t="n">
-        <v>706.2943052432418</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L14" t="n">
-        <v>936.7915875547997</v>
+        <v>1401.924411831626</v>
       </c>
       <c r="M14" t="n">
-        <v>1585.241587554803</v>
+        <v>2050.374411831625</v>
       </c>
       <c r="N14" t="n">
         <v>2233.691587554807</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>405.7156897352959</v>
+        <v>1372.382356401963</v>
       </c>
       <c r="C15" t="n">
-        <v>363.1905256489128</v>
+        <v>1329.85719231558</v>
       </c>
       <c r="D15" t="n">
-        <v>333.9605388835566</v>
+        <v>978.4049833280014</v>
       </c>
       <c r="E15" t="n">
-        <v>84.85511465912413</v>
+        <v>921.1658341605817</v>
       </c>
       <c r="F15" t="n">
-        <v>64.01042542894548</v>
+        <v>578.0989227081807</v>
       </c>
       <c r="G15" t="n">
-        <v>58.00018335964016</v>
+        <v>249.8664584166532</v>
       </c>
       <c r="H15" t="n">
-        <v>52.4</v>
+        <v>244.266275057013</v>
       </c>
       <c r="I15" t="n">
         <v>52.4</v>
@@ -5384,16 +5384,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V15" t="n">
-        <v>1413.982186470323</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W15" t="n">
-        <v>977.2416380765571</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X15" t="n">
-        <v>553.1378608589939</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y15" t="n">
-        <v>471.9344338224946</v>
+        <v>1438.601100489161</v>
       </c>
     </row>
     <row r="16">
@@ -5430,16 +5430,16 @@
         <v>1491.077756743015</v>
       </c>
       <c r="K16" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L16" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M16" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N16" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O16" t="n">
         <v>1112.514307960106</v>
@@ -5512,16 +5512,16 @@
         <v>327.4727226113304</v>
       </c>
       <c r="L17" t="n">
-        <v>936.7915875547997</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M17" t="n">
-        <v>1585.241587554803</v>
+        <v>1206.420004922888</v>
       </c>
       <c r="N17" t="n">
-        <v>2233.691587554807</v>
+        <v>1794.996827913527</v>
       </c>
       <c r="O17" t="n">
-        <v>2410.244759641279</v>
+        <v>1971.55</v>
       </c>
       <c r="P17" t="n">
         <v>2620</v>
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1372.382356401963</v>
+        <v>1147.188141492593</v>
       </c>
       <c r="C18" t="n">
         <v>1104.66297740621</v>
@@ -5576,7 +5576,7 @@
         <v>64.01042542894548</v>
       </c>
       <c r="G18" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H18" t="n">
         <v>52.4</v>
@@ -5609,28 +5609,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2132.917892265885</v>
+        <v>1907.723677356515</v>
       </c>
       <c r="S18" t="n">
-        <v>1998.674143492788</v>
+        <v>1773.479928583418</v>
       </c>
       <c r="T18" t="n">
-        <v>1914.658037974811</v>
+        <v>1689.463823065442</v>
       </c>
       <c r="U18" t="n">
-        <v>1832.679830098122</v>
+        <v>1607.485615188752</v>
       </c>
       <c r="V18" t="n">
-        <v>1736.204408692546</v>
+        <v>1511.010193783176</v>
       </c>
       <c r="W18" t="n">
-        <v>1621.686082521002</v>
+        <v>1396.491867611632</v>
       </c>
       <c r="X18" t="n">
-        <v>1519.804527525661</v>
+        <v>1294.610312616291</v>
       </c>
       <c r="Y18" t="n">
-        <v>1438.601100489161</v>
+        <v>1213.406885579792</v>
       </c>
     </row>
     <row r="19">
@@ -5640,31 +5640,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C19" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D19" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E19" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F19" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G19" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H19" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I19" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J19" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K19" t="n">
         <v>1597.372803794637</v>
@@ -5673,22 +5673,22 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M19" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N19" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O19" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P19" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q19" t="n">
-        <v>466.2233328154397</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R19" t="n">
-        <v>84.56167017509823</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5697,19 +5697,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U19" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V19" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W19" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X19" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y19" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="20">
@@ -5743,25 +5743,25 @@
         <v>52.4</v>
       </c>
       <c r="J20" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K20" t="n">
-        <v>790.1259849731395</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L20" t="n">
-        <v>1438.575984973139</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M20" t="n">
-        <v>2087.025984973143</v>
+        <v>988.9116280297778</v>
       </c>
       <c r="N20" t="n">
-        <v>2087.025984973143</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O20" t="n">
-        <v>2263.579157059615</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P20" t="n">
-        <v>2473.334397418336</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q20" t="n">
         <v>2620</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1147.188141492594</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C21" t="n">
-        <v>782.4407551839881</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D21" t="n">
-        <v>753.2107684186319</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E21" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F21" t="n">
         <v>64.01042542894548</v>
       </c>
       <c r="G21" t="n">
-        <v>58.00018335964016</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H21" t="n">
         <v>52.4</v>
@@ -5858,16 +5858,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V21" t="n">
-        <v>1736.204408692546</v>
+        <v>1413.982186470323</v>
       </c>
       <c r="W21" t="n">
-        <v>1621.686082521002</v>
+        <v>977.2416380765571</v>
       </c>
       <c r="X21" t="n">
-        <v>1519.804527525661</v>
+        <v>553.1378608589939</v>
       </c>
       <c r="Y21" t="n">
-        <v>1213.406885579792</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="22">
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C22" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D22" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E22" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F22" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G22" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H22" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I22" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J22" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K22" t="n">
         <v>1597.372803794637</v>
@@ -5910,7 +5910,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N22" t="n">
         <v>1339.839881046618</v>
@@ -5925,7 +5925,7 @@
         <v>463.3441798078979</v>
       </c>
       <c r="R22" t="n">
-        <v>81.68251716755651</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S22" t="n">
         <v>52.4</v>
@@ -5934,19 +5934,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U22" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V22" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W22" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X22" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y22" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C23" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D23" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E23" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F23" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G23" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032216612</v>
       </c>
       <c r="H23" t="n">
         <v>52.4</v>
@@ -5986,19 +5986,19 @@
         <v>327.4727226113304</v>
       </c>
       <c r="L23" t="n">
-        <v>936.7915875547983</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M23" t="n">
-        <v>1585.241587554803</v>
+        <v>988.9116280297778</v>
       </c>
       <c r="N23" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O23" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P23" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q23" t="n">
         <v>2620</v>
@@ -6007,25 +6007,25 @@
         <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T23" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W23" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X23" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1147.188141492594</v>
+        <v>405.7156897352959</v>
       </c>
       <c r="C24" t="n">
-        <v>782.4407551839881</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D24" t="n">
-        <v>753.2107684186319</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E24" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F24" t="n">
         <v>64.01042542894548</v>
@@ -6080,31 +6080,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2240.946636437805</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2059.873923335154</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S24" t="n">
-        <v>1925.630174562057</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T24" t="n">
-        <v>1841.614069044081</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U24" t="n">
-        <v>1759.635861167391</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V24" t="n">
-        <v>1663.160439761815</v>
+        <v>1413.982186470323</v>
       </c>
       <c r="W24" t="n">
-        <v>1548.642113590271</v>
+        <v>977.2416380765571</v>
       </c>
       <c r="X24" t="n">
-        <v>1446.76055859493</v>
+        <v>553.1378608589939</v>
       </c>
       <c r="Y24" t="n">
-        <v>1365.557131558431</v>
+        <v>471.9344338224946</v>
       </c>
     </row>
     <row r="25">
@@ -6144,25 +6144,25 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L25" t="n">
-        <v>1591.155096928856</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M25" t="n">
-        <v>1492.275360291076</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N25" t="n">
-        <v>1339.839881046618</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O25" t="n">
-        <v>1109.635154952564</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P25" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R25" t="n">
-        <v>81.68251716755651</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S25" t="n">
         <v>52.4</v>
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C26" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D26" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E26" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F26" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G26" t="n">
         <v>127.0464193797368</v>
@@ -6223,19 +6223,19 @@
         <v>327.4727226113304</v>
       </c>
       <c r="L26" t="n">
-        <v>936.7915875548066</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M26" t="n">
-        <v>1585.241587554807</v>
+        <v>988.9116280297778</v>
       </c>
       <c r="N26" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O26" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P26" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q26" t="n">
         <v>2620</v>
@@ -6262,7 +6262,7 @@
         <v>966.4093570991351</v>
       </c>
       <c r="Y26" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="27">
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1050.160134179741</v>
+        <v>1147.188141492593</v>
       </c>
       <c r="C27" t="n">
-        <v>685.4127478711353</v>
+        <v>1104.66297740621</v>
       </c>
       <c r="D27" t="n">
-        <v>430.9885461964096</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E27" t="n">
-        <v>84.85511465912413</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F27" t="n">
         <v>64.01042542894548</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H27" t="n">
         <v>52.4</v>
@@ -6332,16 +6332,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V27" t="n">
-        <v>1736.204408692546</v>
+        <v>1511.010193783176</v>
       </c>
       <c r="W27" t="n">
-        <v>1299.46386029878</v>
+        <v>1396.491867611632</v>
       </c>
       <c r="X27" t="n">
-        <v>1197.582305303438</v>
+        <v>1294.610312616291</v>
       </c>
       <c r="Y27" t="n">
-        <v>1116.378878266939</v>
+        <v>1213.406885579792</v>
       </c>
     </row>
     <row r="28">
@@ -6351,31 +6351,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H28" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K28" t="n">
         <v>1597.372803794637</v>
@@ -6384,7 +6384,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M28" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N28" t="n">
         <v>1339.839881046618</v>
@@ -6396,10 +6396,10 @@
         <v>818.3161660963807</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R28" t="n">
-        <v>81.68251716755645</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S28" t="n">
         <v>52.4</v>
@@ -6408,19 +6408,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V28" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X28" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C29" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D29" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E29" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F29" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G29" t="n">
         <v>127.0464193797368</v>
@@ -6466,13 +6466,13 @@
         <v>1864.577674193434</v>
       </c>
       <c r="N29" t="n">
-        <v>1864.577674193434</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O29" t="n">
-        <v>2041.130846279907</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P29" t="n">
-        <v>2250.886086638628</v>
+        <v>2620</v>
       </c>
       <c r="Q29" t="n">
         <v>2620</v>
@@ -6487,19 +6487,19 @@
         <v>2212.479660135798</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W29" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X29" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>727.9379119575183</v>
+        <v>405.7156897352959</v>
       </c>
       <c r="C30" t="n">
-        <v>685.4127478711351</v>
+        <v>363.1905256489127</v>
       </c>
       <c r="D30" t="n">
-        <v>430.9885461964096</v>
+        <v>333.9605388835565</v>
       </c>
       <c r="E30" t="n">
-        <v>84.85511465912413</v>
+        <v>310.0493295684932</v>
       </c>
       <c r="F30" t="n">
         <v>64.01042542894548</v>
       </c>
       <c r="G30" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H30" t="n">
         <v>52.4</v>
@@ -6572,13 +6572,13 @@
         <v>1413.982186470323</v>
       </c>
       <c r="W30" t="n">
-        <v>977.2416380765571</v>
+        <v>1299.463860298779</v>
       </c>
       <c r="X30" t="n">
-        <v>875.3600830812162</v>
+        <v>875.3600830812161</v>
       </c>
       <c r="Y30" t="n">
-        <v>794.1566560447169</v>
+        <v>471.9344338224945</v>
       </c>
     </row>
     <row r="31">
@@ -6588,31 +6588,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H31" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K31" t="n">
         <v>1597.372803794637</v>
@@ -6633,10 +6633,10 @@
         <v>821.1953191039224</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.2233328154397</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R31" t="n">
-        <v>84.56167017509823</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S31" t="n">
         <v>52.4</v>
@@ -6645,19 +6645,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V31" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X31" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="32">
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C32" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D32" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E32" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F32" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G32" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032216612</v>
       </c>
       <c r="H32" t="n">
         <v>52.4</v>
@@ -6694,22 +6694,22 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K32" t="n">
-        <v>327.4727226113304</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L32" t="n">
-        <v>936.791587554806</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M32" t="n">
-        <v>1585.241587554807</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="N32" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O32" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P32" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q32" t="n">
         <v>2620</v>
@@ -6718,25 +6718,25 @@
         <v>2620</v>
       </c>
       <c r="S32" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T32" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U32" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W32" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X32" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>372.3877498829398</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C33" t="n">
-        <v>329.8625857965566</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D33" t="n">
-        <v>300.6325990312004</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E33" t="n">
-        <v>276.7213897161371</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F33" t="n">
-        <v>255.8767004859585</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G33" t="n">
-        <v>249.8664584166532</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H33" t="n">
-        <v>244.266275057013</v>
+        <v>52.4</v>
       </c>
       <c r="I33" t="n">
         <v>52.4</v>
@@ -6791,31 +6791,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2313.990605368536</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R33" t="n">
-        <v>2132.917892265885</v>
+        <v>1737.651701112932</v>
       </c>
       <c r="S33" t="n">
-        <v>1998.674143492788</v>
+        <v>1451.257706361196</v>
       </c>
       <c r="T33" t="n">
-        <v>1914.658037974811</v>
+        <v>1367.24160084322</v>
       </c>
       <c r="U33" t="n">
-        <v>1510.457607875899</v>
+        <v>1285.26339296653</v>
       </c>
       <c r="V33" t="n">
-        <v>1380.654246617967</v>
+        <v>866.5657493387318</v>
       </c>
       <c r="W33" t="n">
-        <v>943.913698224201</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X33" t="n">
-        <v>519.8099210066378</v>
+        <v>327.9436459496247</v>
       </c>
       <c r="Y33" t="n">
-        <v>438.6064939701384</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="34">
@@ -6825,31 +6825,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H34" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J34" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K34" t="n">
         <v>1597.372803794637</v>
@@ -6870,10 +6870,10 @@
         <v>821.1953191039224</v>
       </c>
       <c r="Q34" t="n">
-        <v>466.2233328154396</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R34" t="n">
-        <v>84.56167017509824</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S34" t="n">
         <v>52.4</v>
@@ -6882,19 +6882,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V34" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W34" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X34" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="35">
@@ -6931,22 +6931,22 @@
         <v>119.1959849731395</v>
       </c>
       <c r="K35" t="n">
-        <v>304.9927226113305</v>
+        <v>489.4559849731395</v>
       </c>
       <c r="L35" t="n">
-        <v>535.4900049228883</v>
+        <v>719.9532672846973</v>
       </c>
       <c r="M35" t="n">
-        <v>535.4900049228884</v>
+        <v>1090.213267284697</v>
       </c>
       <c r="N35" t="n">
-        <v>905.7500049228884</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="O35" t="n">
-        <v>1082.303177009361</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P35" t="n">
-        <v>1292.058417368081</v>
+        <v>1496</v>
       </c>
       <c r="Q35" t="n">
         <v>1496</v>
@@ -6955,10 +6955,10 @@
         <v>1496</v>
       </c>
       <c r="S35" t="n">
-        <v>1434.457487638385</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T35" t="n">
-        <v>1249.38969024747</v>
+        <v>1246.055417711555</v>
       </c>
       <c r="U35" t="n">
         <v>994.7399262092307</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>919.3719155818769</v>
+        <v>564.8531865094139</v>
       </c>
       <c r="C36" t="n">
-        <v>919.3719155818769</v>
+        <v>564.8531865094139</v>
       </c>
       <c r="D36" t="n">
-        <v>567.9197065942985</v>
+        <v>564.8531865094139</v>
       </c>
       <c r="E36" t="n">
-        <v>221.786275057013</v>
+        <v>564.8531865094139</v>
       </c>
       <c r="F36" t="n">
         <v>221.786275057013</v>
@@ -7010,16 +7010,16 @@
         <v>227.711345930016</v>
       </c>
       <c r="K36" t="n">
-        <v>250.1782010228462</v>
+        <v>543.0996394772296</v>
       </c>
       <c r="L36" t="n">
-        <v>527.4420010172646</v>
+        <v>599.927050901758</v>
       </c>
       <c r="M36" t="n">
-        <v>527.4420010172646</v>
+        <v>884.0224426446173</v>
       </c>
       <c r="N36" t="n">
-        <v>863.9779994927574</v>
+        <v>1188.111259659669</v>
       </c>
       <c r="O36" t="n">
         <v>1234.237999492757</v>
@@ -7031,28 +7031,28 @@
         <v>1422.95603106927</v>
       </c>
       <c r="R36" t="n">
-        <v>1320.671196754497</v>
+        <v>1045.178253291492</v>
       </c>
       <c r="S36" t="n">
-        <v>1006.71768585823</v>
+        <v>989.7223833062737</v>
       </c>
       <c r="T36" t="n">
-        <v>1001.489459128133</v>
+        <v>984.4941565761759</v>
       </c>
       <c r="U36" t="n">
-        <v>998.2991300393219</v>
+        <v>981.3038274873652</v>
       </c>
       <c r="V36" t="n">
-        <v>980.6115874216248</v>
+        <v>963.6162848696681</v>
       </c>
       <c r="W36" t="n">
-        <v>944.8811400379597</v>
+        <v>590.3624109654967</v>
       </c>
       <c r="X36" t="n">
-        <v>921.7874638304975</v>
+        <v>567.2687347580345</v>
       </c>
       <c r="Y36" t="n">
-        <v>919.3719155818769</v>
+        <v>564.8531865094139</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>880.3740993321859</v>
+        <v>286.7681286904857</v>
       </c>
       <c r="C37" t="n">
-        <v>880.3740993321859</v>
+        <v>409.8001345089215</v>
       </c>
       <c r="D37" t="n">
-        <v>880.3740993321859</v>
+        <v>520.1492786339215</v>
       </c>
       <c r="E37" t="n">
-        <v>880.3740993321859</v>
+        <v>635.0081828453345</v>
       </c>
       <c r="F37" t="n">
-        <v>1001.765071924121</v>
+        <v>756.39915543727</v>
       </c>
       <c r="G37" t="n">
-        <v>1001.765071924121</v>
+        <v>907.4909065700569</v>
       </c>
       <c r="H37" t="n">
-        <v>1001.765071924121</v>
+        <v>907.4909065700569</v>
       </c>
       <c r="I37" t="n">
-        <v>1001.765071924121</v>
+        <v>907.4909065700569</v>
       </c>
       <c r="J37" t="n">
         <v>1066.665307034026</v>
@@ -7113,25 +7113,25 @@
         <v>29.92</v>
       </c>
       <c r="S37" t="n">
-        <v>75.61834706138623</v>
+        <v>29.92</v>
       </c>
       <c r="T37" t="n">
-        <v>75.61834706138623</v>
+        <v>29.92</v>
       </c>
       <c r="U37" t="n">
-        <v>319.235277076722</v>
+        <v>29.92</v>
       </c>
       <c r="V37" t="n">
-        <v>515.086669962668</v>
+        <v>29.92</v>
       </c>
       <c r="W37" t="n">
-        <v>515.086669962668</v>
+        <v>29.92</v>
       </c>
       <c r="X37" t="n">
-        <v>663.1474609868615</v>
+        <v>177.9807910241935</v>
       </c>
       <c r="Y37" t="n">
-        <v>771.5867616658937</v>
+        <v>177.9807910241935</v>
       </c>
     </row>
     <row r="38">
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113.806583727033</v>
+        <v>117.1408562629478</v>
       </c>
       <c r="C38" t="n">
-        <v>60.80195923916038</v>
+        <v>64.13623177507512</v>
       </c>
       <c r="D38" t="n">
-        <v>47.32806455244342</v>
+        <v>50.66233708835816</v>
       </c>
       <c r="E38" t="n">
-        <v>43.2246708187939</v>
+        <v>43.22467081879388</v>
       </c>
       <c r="F38" t="n">
-        <v>35.25534889150919</v>
+        <v>35.25534889150917</v>
       </c>
       <c r="G38" t="n">
         <v>29.92</v>
@@ -7174,16 +7174,16 @@
         <v>535.4900049228883</v>
       </c>
       <c r="M38" t="n">
-        <v>535.4900049228884</v>
+        <v>905.7500049228884</v>
       </c>
       <c r="N38" t="n">
-        <v>739.431587554807</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="O38" t="n">
-        <v>915.9847596412797</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P38" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q38" t="n">
         <v>1496</v>
@@ -7198,19 +7198,19 @@
         <v>1246.055417711555</v>
       </c>
       <c r="U38" t="n">
-        <v>991.405653673316</v>
+        <v>994.7399262092307</v>
       </c>
       <c r="V38" t="n">
-        <v>756.2025989593525</v>
+        <v>759.5368714952672</v>
       </c>
       <c r="W38" t="n">
-        <v>512.3910070594054</v>
+        <v>515.7252795953201</v>
       </c>
       <c r="X38" t="n">
-        <v>315.1366298264077</v>
+        <v>318.4709023623224</v>
       </c>
       <c r="Y38" t="n">
-        <v>199.6644756013507</v>
+        <v>202.9987481372655</v>
       </c>
     </row>
     <row r="39">
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>800.0917787151479</v>
+        <v>908.8661950295435</v>
       </c>
       <c r="C39" t="n">
-        <v>800.0917787151479</v>
+        <v>544.1188087209382</v>
       </c>
       <c r="D39" t="n">
-        <v>448.6395697275695</v>
+        <v>544.1188087209382</v>
       </c>
       <c r="E39" t="n">
-        <v>102.506138190284</v>
+        <v>544.1188087209382</v>
       </c>
       <c r="F39" t="n">
-        <v>102.506138190284</v>
+        <v>544.1188087209382</v>
       </c>
       <c r="G39" t="n">
-        <v>102.506138190284</v>
+        <v>215.8863444294107</v>
       </c>
       <c r="H39" t="n">
         <v>29.92</v>
@@ -7244,19 +7244,19 @@
         <v>29.92</v>
       </c>
       <c r="J39" t="n">
-        <v>29.92</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K39" t="n">
-        <v>345.3082935472136</v>
+        <v>543.0996394772296</v>
       </c>
       <c r="L39" t="n">
-        <v>579.8826077498982</v>
+        <v>599.927050901758</v>
       </c>
       <c r="M39" t="n">
-        <v>863.9779994927574</v>
+        <v>599.927050901758</v>
       </c>
       <c r="N39" t="n">
-        <v>863.9779994927574</v>
+        <v>936.4630493772507</v>
       </c>
       <c r="O39" t="n">
         <v>1234.237999492757</v>
@@ -7265,31 +7265,31 @@
         <v>1496</v>
       </c>
       <c r="Q39" t="n">
-        <v>1422.95603106927</v>
+        <v>1496</v>
       </c>
       <c r="R39" t="n">
-        <v>1320.671196754497</v>
+        <v>1393.715165685228</v>
       </c>
       <c r="S39" t="n">
-        <v>1265.215326769279</v>
+        <v>1338.259295700009</v>
       </c>
       <c r="T39" t="n">
-        <v>1259.987100039182</v>
+        <v>1333.031068969912</v>
       </c>
       <c r="U39" t="n">
-        <v>1256.796770950371</v>
+        <v>1329.840739881101</v>
       </c>
       <c r="V39" t="n">
-        <v>1239.109228332674</v>
+        <v>1312.153197263404</v>
       </c>
       <c r="W39" t="n">
-        <v>1203.378780949008</v>
+        <v>934.3754194856263</v>
       </c>
       <c r="X39" t="n">
-        <v>1180.285104741546</v>
+        <v>911.2817432781641</v>
       </c>
       <c r="Y39" t="n">
-        <v>1177.869556492926</v>
+        <v>908.8661950295435</v>
       </c>
     </row>
     <row r="40">
@@ -7299,34 +7299,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29.92</v>
+        <v>469.3883229012818</v>
       </c>
       <c r="C40" t="n">
-        <v>29.92</v>
+        <v>469.3883229012818</v>
       </c>
       <c r="D40" t="n">
-        <v>29.92</v>
+        <v>579.7374670262818</v>
       </c>
       <c r="E40" t="n">
-        <v>144.778904211413</v>
+        <v>579.7374670262818</v>
       </c>
       <c r="F40" t="n">
-        <v>266.1698768033485</v>
+        <v>579.7374670262818</v>
       </c>
       <c r="G40" t="n">
-        <v>417.2616279361354</v>
+        <v>730.8292181590687</v>
       </c>
       <c r="H40" t="n">
-        <v>589.6334055545494</v>
+        <v>903.2009957774826</v>
       </c>
       <c r="I40" t="n">
-        <v>827.4994917037471</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="J40" t="n">
-        <v>838.9048292414443</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="K40" t="n">
-        <v>1022.419876293067</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="L40" t="n">
         <v>1066.665307034026</v>
@@ -7335,13 +7335,13 @@
         <v>1046.573449184125</v>
       </c>
       <c r="N40" t="n">
-        <v>972.9258487275466</v>
+        <v>972.9258487275464</v>
       </c>
       <c r="O40" t="n">
-        <v>821.5090014213715</v>
+        <v>821.5090014213713</v>
       </c>
       <c r="P40" t="n">
-        <v>608.9778913530666</v>
+        <v>608.9778913530665</v>
       </c>
       <c r="Q40" t="n">
         <v>332.7937838524626</v>
@@ -7356,19 +7356,19 @@
         <v>29.92</v>
       </c>
       <c r="U40" t="n">
-        <v>29.92</v>
+        <v>273.5369300153358</v>
       </c>
       <c r="V40" t="n">
-        <v>29.92</v>
+        <v>469.3883229012818</v>
       </c>
       <c r="W40" t="n">
-        <v>29.92</v>
+        <v>469.3883229012818</v>
       </c>
       <c r="X40" t="n">
-        <v>29.92</v>
+        <v>469.3883229012818</v>
       </c>
       <c r="Y40" t="n">
-        <v>29.92</v>
+        <v>469.3883229012818</v>
       </c>
     </row>
     <row r="41">
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.92</v>
+        <v>442.0105017516437</v>
       </c>
       <c r="C41" t="n">
-        <v>29.92</v>
+        <v>283.9553722132661</v>
       </c>
       <c r="D41" t="n">
-        <v>29.92</v>
+        <v>165.430972476044</v>
       </c>
       <c r="E41" t="n">
-        <v>29.92</v>
+        <v>52.94280115597469</v>
       </c>
       <c r="F41" t="n">
-        <v>29.92</v>
+        <v>52.94280115597469</v>
       </c>
       <c r="G41" t="n">
         <v>29.92</v>
@@ -7432,22 +7432,22 @@
         <v>1496</v>
       </c>
       <c r="T41" t="n">
-        <v>1381.040808087168</v>
+        <v>1496</v>
       </c>
       <c r="U41" t="n">
-        <v>1021.340538998424</v>
+        <v>1496</v>
       </c>
       <c r="V41" t="n">
-        <v>681.0869792339549</v>
+        <v>1155.746440235531</v>
       </c>
       <c r="W41" t="n">
-        <v>332.2248822835028</v>
+        <v>1155.746440235531</v>
       </c>
       <c r="X41" t="n">
-        <v>29.92</v>
+        <v>853.4415579520285</v>
       </c>
       <c r="Y41" t="n">
-        <v>29.92</v>
+        <v>632.9188986764665</v>
       </c>
     </row>
     <row r="42">
@@ -7472,7 +7472,7 @@
         <v>94.05567795419802</v>
       </c>
       <c r="G42" t="n">
-        <v>61.78280962226643</v>
+        <v>61.78280962226644</v>
       </c>
       <c r="H42" t="n">
         <v>29.92</v>
@@ -7487,13 +7487,13 @@
         <v>543.0996394772296</v>
       </c>
       <c r="L42" t="n">
-        <v>863.9779994927574</v>
+        <v>851.5752611841763</v>
       </c>
       <c r="M42" t="n">
-        <v>863.9779994927574</v>
+        <v>851.5752611841763</v>
       </c>
       <c r="N42" t="n">
-        <v>863.9779994927574</v>
+        <v>1188.111259659669</v>
       </c>
       <c r="O42" t="n">
         <v>1234.237999492757</v>
@@ -7502,7 +7502,7 @@
         <v>1496</v>
       </c>
       <c r="Q42" t="n">
-        <v>1496</v>
+        <v>1493.589117731894</v>
       </c>
       <c r="R42" t="n">
         <v>1286.253778366616</v>
@@ -7569,22 +7569,22 @@
         <v>1163.052803794637</v>
       </c>
       <c r="M43" t="n">
-        <v>1163.052803794637</v>
+        <v>1037.910440894231</v>
       </c>
       <c r="N43" t="n">
-        <v>1163.052803794637</v>
+        <v>1037.910440894231</v>
       </c>
       <c r="O43" t="n">
-        <v>906.5854514379571</v>
+        <v>781.4430885375507</v>
       </c>
       <c r="P43" t="n">
-        <v>589.0038363191472</v>
+        <v>463.8614734187408</v>
       </c>
       <c r="Q43" t="n">
-        <v>211.2260585413694</v>
+        <v>88.34429643772449</v>
       </c>
       <c r="R43" t="n">
-        <v>88.34429643772452</v>
+        <v>88.34429643772449</v>
       </c>
       <c r="S43" t="n">
         <v>29.92</v>
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>226.661414920773</v>
+        <v>612.3367715680781</v>
       </c>
       <c r="C44" t="n">
-        <v>68.60628538239524</v>
+        <v>454.2816420297004</v>
       </c>
       <c r="D44" t="n">
-        <v>29.92</v>
+        <v>335.7572422924784</v>
       </c>
       <c r="E44" t="n">
-        <v>29.92</v>
+        <v>223.2690709724091</v>
       </c>
       <c r="F44" t="n">
-        <v>29.92</v>
+        <v>110.2492439946193</v>
       </c>
       <c r="G44" t="n">
         <v>29.92</v>
@@ -7651,13 +7651,13 @@
         <v>535.4900049228884</v>
       </c>
       <c r="N44" t="n">
-        <v>905.7500049228884</v>
+        <v>578.9268279135274</v>
       </c>
       <c r="O44" t="n">
-        <v>1082.303177009361</v>
+        <v>755.48</v>
       </c>
       <c r="P44" t="n">
-        <v>1292.058417368081</v>
+        <v>1125.74</v>
       </c>
       <c r="Q44" t="n">
         <v>1496</v>
@@ -7666,25 +7666,25 @@
         <v>1496</v>
       </c>
       <c r="S44" t="n">
-        <v>1496</v>
+        <v>1326.072710051966</v>
       </c>
       <c r="T44" t="n">
-        <v>1496</v>
+        <v>1326.072710051966</v>
       </c>
       <c r="U44" t="n">
-        <v>1136.299730911256</v>
+        <v>1326.072710051966</v>
       </c>
       <c r="V44" t="n">
-        <v>796.0461711467871</v>
+        <v>1326.072710051966</v>
       </c>
       <c r="W44" t="n">
-        <v>447.184074196335</v>
+        <v>1326.072710051966</v>
       </c>
       <c r="X44" t="n">
-        <v>447.184074196335</v>
+        <v>1023.767827768463</v>
       </c>
       <c r="Y44" t="n">
-        <v>226.661414920773</v>
+        <v>803.2451684929009</v>
       </c>
     </row>
     <row r="45">
@@ -7724,16 +7724,16 @@
         <v>543.0996394772296</v>
       </c>
       <c r="L45" t="n">
-        <v>904.0158679168098</v>
+        <v>913.3596394772296</v>
       </c>
       <c r="M45" t="n">
-        <v>1188.111259659669</v>
+        <v>1197.455031220089</v>
       </c>
       <c r="N45" t="n">
-        <v>1188.111259659669</v>
+        <v>1405.070464381813</v>
       </c>
       <c r="O45" t="n">
-        <v>1234.237999492757</v>
+        <v>1451.197204214901</v>
       </c>
       <c r="P45" t="n">
         <v>1496</v>
@@ -7803,25 +7803,25 @@
         <v>1163.052803794637</v>
       </c>
       <c r="L46" t="n">
-        <v>1130.57247066623</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="M46" t="n">
-        <v>1130.57247066623</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="N46" t="n">
-        <v>951.8743651591461</v>
+        <v>984.3546982875536</v>
       </c>
       <c r="O46" t="n">
-        <v>951.8743651591461</v>
+        <v>727.8873459308734</v>
       </c>
       <c r="P46" t="n">
-        <v>634.2927500403362</v>
+        <v>410.3057308120635</v>
       </c>
       <c r="Q46" t="n">
-        <v>256.5149722625583</v>
+        <v>32.52795303428564</v>
       </c>
       <c r="R46" t="n">
-        <v>88.34429643772449</v>
+        <v>29.92</v>
       </c>
       <c r="S46" t="n">
         <v>29.92</v>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>472.2608914614128</v>
+        <v>714.2808456769349</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O2" t="n">
         <v>375.1590153027356</v>
@@ -7985,7 +7985,7 @@
         <v>315.3213213472141</v>
       </c>
       <c r="Q2" t="n">
-        <v>370.5618244726559</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,13 +8201,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>183.3412755627362</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>846.2608914614127</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,16 +8441,16 @@
         <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>707.7620966723902</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>311.8831458198699</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>382.6480632645561</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>940.1988562855377</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N11" t="n">
-        <v>868.9937721401911</v>
+        <v>821.3370988185948</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>382.648063264557</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>422.1744623115578</v>
       </c>
       <c r="M14" t="n">
-        <v>940.1988562855372</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N14" t="n">
-        <v>868.9937721401907</v>
+        <v>399.1626365070372</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9155,19 +9155,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>382.648063264557</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>940.1988562855372</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N17" t="n">
-        <v>868.9937721401907</v>
+        <v>808.5158155650747</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>443.1260198396765</v>
       </c>
       <c r="Q17" t="n">
         <v>13.49857879984722</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>467.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>422.1744623115576</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>940.1988562855372</v>
+        <v>290.1886884942146</v>
       </c>
       <c r="N20" t="n">
-        <v>213.993772140187</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>161.6456521146596</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9629,13 +9629,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>382.6480632645556</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>940.1988562855379</v>
+        <v>720.4934250803714</v>
       </c>
       <c r="N23" t="n">
-        <v>868.9937721401916</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9866,10 +9866,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>382.648063264564</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>940.1988562855336</v>
+        <v>720.4934250803714</v>
       </c>
       <c r="N26" t="n">
         <v>868.993772140187</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10109,7 +10109,7 @@
         <v>285.1988562855334</v>
       </c>
       <c r="N29" t="n">
-        <v>213.993772140187</v>
+        <v>586.8361088688462</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>386.3409155285062</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L32" t="n">
-        <v>382.6480632645636</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M32" t="n">
-        <v>940.198856285534</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N32" t="n">
-        <v>868.9937721401875</v>
+        <v>414.7873509852764</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,16 +10574,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>186.326527638191</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>285.1988562855334</v>
+        <v>659.1988562855333</v>
       </c>
       <c r="N35" t="n">
-        <v>587.993772140187</v>
+        <v>233.6688431200957</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>219.5001774179469</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10653,19 +10653,19 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>222.6630187574647</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>452.633596403228</v>
       </c>
       <c r="O36" t="n">
-        <v>327.4073335019309</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10817,7 +10817,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>285.1988562855334</v>
+        <v>659.1988562855333</v>
       </c>
       <c r="N38" t="n">
         <v>419.9953707582866</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>387.4985787998472</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10887,22 +10887,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>27.675503614641</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>179.5423260385417</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>471.6948204301074</v>
+        <v>184.7297782656032</v>
       </c>
       <c r="N39" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>327.4073335019309</v>
+        <v>254.1901113963821</v>
       </c>
       <c r="P39" t="n">
         <v>219.1507118405495</v>
@@ -11130,16 +11130,16 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>266.7181298898984</v>
+        <v>254.1901113963822</v>
       </c>
       <c r="M42" t="n">
         <v>184.7297782656032</v>
       </c>
       <c r="N42" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>327.4073335019309</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11294,16 +11294,16 @@
         <v>285.1988562855334</v>
       </c>
       <c r="N44" t="n">
-        <v>587.993772140187</v>
+        <v>257.8693509186103</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>162.1260198396764</v>
       </c>
       <c r="Q44" t="n">
-        <v>219.5001774179469</v>
+        <v>387.4985787998472</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11367,19 +11367,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>307.1604212273252</v>
+        <v>316.5985743186583</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>145.473175175903</v>
+        <v>355.1857339251194</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.591615728102624e-12</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.154631945610163e-12</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2.850361477466112</v>
+        <v>2.850361477466563</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.850361477465901</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23657,7 +23657,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6960849964948983</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.850361477466748</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.696084996494875</v>
+        <v>0.6960849964948983</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.850361477466322</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.6960849964948608</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.850361477466352</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.850361477466322</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.696084996494875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24611,13 +24611,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.85036147746635</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0.6960849964950739</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.850361477466563</v>
+        <v>2.850361477466352</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2.850361477466352</v>
+        <v>2.850361477466563</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -25170,13 +25170,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
         <v>3.300929810555573</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -25365,7 +25365,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3.300929810555617</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.30092981055563</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>156.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>111.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>109.2819954025941</v>
+        <v>86.48942225817916</v>
       </c>
       <c r="H41" t="n">
-        <v>99.89995518593946</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25647,22 +25647,22 @@
         <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
-        <v>173.4075194233024</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>218.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25781,10 +25781,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712345</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M43" t="n">
-        <v>123.8909392714024</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>176.9111244520127</v>
@@ -25796,10 +25796,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.422266425597968</v>
+        <v>5.660261214391824</v>
       </c>
       <c r="R43" t="n">
-        <v>282.1921015313295</v>
+        <v>403.845046013938</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -25830,22 +25830,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>79.0397332112785</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>109.2819954025941</v>
+        <v>29.756043847921</v>
       </c>
       <c r="H44" t="n">
         <v>99.89995518593948</v>
@@ -25881,22 +25881,22 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -26018,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M46" t="n">
         <v>123.8909392714024</v>
@@ -26027,7 +26027,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>253.9026788331133</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -26036,10 +26036,10 @@
         <v>3.422266425597996</v>
       </c>
       <c r="R46" t="n">
-        <v>237.3560769473525</v>
+        <v>401.2631725099952</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26272,7 +26272,7 @@
         <v>1164923.76230765</v>
       </c>
       <c r="C2" t="n">
-        <v>1164923.76230765</v>
+        <v>1164923.762307649</v>
       </c>
       <c r="D2" t="n">
         <v>1164923.76230765</v>
@@ -26284,22 +26284,22 @@
         <v>1164809.231544558</v>
       </c>
       <c r="G2" t="n">
+        <v>1164809.231544558</v>
+      </c>
+      <c r="H2" t="n">
         <v>1164809.231544557</v>
       </c>
-      <c r="H2" t="n">
-        <v>1164809.231544558</v>
-      </c>
       <c r="I2" t="n">
-        <v>1164809.231544558</v>
+        <v>1164809.231544559</v>
       </c>
       <c r="J2" t="n">
+        <v>1164809.231544559</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1164809.231544559</v>
+      </c>
+      <c r="L2" t="n">
         <v>1164809.231544557</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1164809.231544557</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1164809.231544558</v>
       </c>
       <c r="M2" t="n">
         <v>1164680.714845699</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101185</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.2919515911</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687437</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689994</v>
+        <v>503256.5379432672</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285004</v>
+        <v>501580.9146027683</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045217</v>
+        <v>499902.9383787895</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.75052655</v>
+        <v>498222.5921008178</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963753</v>
+        <v>496539.8583706431</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842147</v>
+        <v>522371.0444804642</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731496</v>
+        <v>520403.913769399</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155932</v>
+        <v>447670.9673118427</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523478</v>
+        <v>446003.2126485973</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>272816.1860975315</v>
+        <v>273015.5007527465</v>
       </c>
       <c r="C6" t="n">
-        <v>505923.1082850202</v>
+        <v>506122.4229402338</v>
       </c>
       <c r="D6" t="n">
-        <v>507934.7557008445</v>
+        <v>508134.070356059</v>
       </c>
       <c r="E6" t="n">
-        <v>-30783.99692402416</v>
+        <v>-30589.83849829176</v>
       </c>
       <c r="F6" t="n">
-        <v>583371.6685758147</v>
+        <v>583565.8270015466</v>
       </c>
       <c r="G6" t="n">
-        <v>585042.6367714333</v>
+        <v>585236.7951971669</v>
       </c>
       <c r="H6" t="n">
-        <v>586715.9241755587</v>
+        <v>586910.08260129</v>
       </c>
       <c r="I6" t="n">
-        <v>588391.5475160577</v>
+        <v>588585.7059417904</v>
       </c>
       <c r="J6" t="n">
-        <v>203221.523740035</v>
+        <v>203415.6821657692</v>
       </c>
       <c r="K6" t="n">
-        <v>591749.8700180068</v>
+        <v>591944.0284437408</v>
       </c>
       <c r="L6" t="n">
-        <v>593432.6037481828</v>
+        <v>593626.7621739141</v>
       </c>
       <c r="M6" t="n">
-        <v>515675.0602614841</v>
+        <v>515794.4773652349</v>
       </c>
       <c r="N6" t="n">
-        <v>580042.190972549</v>
+        <v>580161.6080763002</v>
       </c>
       <c r="O6" t="n">
-        <v>368882.6221849647</v>
+        <v>369002.0392887153</v>
       </c>
       <c r="P6" t="n">
-        <v>542550.3768482099</v>
+        <v>542669.7939519607</v>
       </c>
     </row>
   </sheetData>
@@ -27008,7 +27008,7 @@
         <v>78</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>215</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>398.2013121321719</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>223.3220918649895</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27515,13 +27515,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>209.054706265568</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -27572,10 +27572,10 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
+        <v>40.51066719152016</v>
+      </c>
+      <c r="W3" t="n">
         <v>400</v>
-      </c>
-      <c r="W3" t="n">
-        <v>267.9931886806949</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27594,7 +27594,7 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>171.1020457840527</v>
       </c>
       <c r="J4" t="n">
-        <v>235.6107148713897</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>358.0389230415193</v>
       </c>
       <c r="L4" t="n">
         <v>396.2015953708939</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
+        <v>209.2386648669134</v>
+      </c>
+      <c r="U4" t="n">
+        <v>150.9483584875727</v>
+      </c>
+      <c r="V4" t="n">
         <v>400</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>400</v>
       </c>
-      <c r="V4" t="n">
-        <v>199.1703102162162</v>
-      </c>
-      <c r="W4" t="n">
-        <v>226.3728098387097</v>
-      </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27812,13 +27812,13 @@
         <v>40.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>265.77400180979</v>
+        <v>64.90045890580495</v>
       </c>
     </row>
     <row r="7">
@@ -27840,19 +27840,19 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>282.6683395005033</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J7" t="n">
-        <v>195.7984179116122</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
         <v>267.1509377355693</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T7" t="n">
         <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27995,13 +27995,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>330.0491815260438</v>
@@ -28034,7 +28034,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>372.221355449421</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28043,16 +28043,16 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>58.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>79.82380753326788</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28071,28 +28071,28 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>336.5432435627184</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>396.2015953708939</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>328.1499235951626</v>
       </c>
     </row>
     <row r="11">
@@ -28226,7 +28226,7 @@
         <v>319</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="D12" t="n">
         <v>319</v>
@@ -28238,10 +28238,10 @@
         <v>319</v>
       </c>
       <c r="G12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>189.9476123064429</v>
@@ -28271,13 +28271,13 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
-        <v>96.05772723972416</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>319</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="U12" t="n">
         <v>319</v>
@@ -28289,7 +28289,7 @@
         <v>319</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y12" t="n">
         <v>319</v>
@@ -28362,7 +28362,7 @@
         <v>319</v>
       </c>
       <c r="V13" t="n">
-        <v>319.0000000000001</v>
+        <v>319</v>
       </c>
       <c r="W13" t="n">
         <v>319</v>
@@ -28466,22 +28466,22 @@
         <v>319</v>
       </c>
       <c r="D15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>96.0577272397245</v>
+        <v>286.005339546167</v>
       </c>
       <c r="F15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>319</v>
       </c>
       <c r="I15" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28520,13 +28520,13 @@
         <v>319</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y15" t="n">
         <v>319</v>
@@ -28566,7 +28566,7 @@
         <v>319</v>
       </c>
       <c r="K16" t="n">
-        <v>319.0000000000005</v>
+        <v>319</v>
       </c>
       <c r="L16" t="n">
         <v>319</v>
@@ -28700,7 +28700,7 @@
         <v>319</v>
       </c>
       <c r="C18" t="n">
-        <v>96.05772723972427</v>
+        <v>319</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -28745,7 +28745,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R18" t="n">
-        <v>319</v>
+        <v>96.05772723972416</v>
       </c>
       <c r="S18" t="n">
         <v>319</v>
@@ -28937,16 +28937,16 @@
         <v>319</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D21" t="n">
         <v>319</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G21" t="n">
         <v>319</v>
@@ -28994,13 +28994,13 @@
         <v>319</v>
       </c>
       <c r="V21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>96.05772723972444</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.3712564811476</v>
+        <v>319</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>96.0577272397245</v>
       </c>
       <c r="D24" t="n">
         <v>319</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G24" t="n">
         <v>319</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R24" t="n">
         <v>319</v>
@@ -29231,13 +29231,13 @@
         <v>319</v>
       </c>
       <c r="V24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>319</v>
@@ -29411,16 +29411,16 @@
         <v>319</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D27" t="n">
-        <v>96.05772723972427</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>319</v>
@@ -29468,10 +29468,10 @@
         <v>319</v>
       </c>
       <c r="V27" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X27" t="n">
         <v>319</v>
@@ -29651,13 +29651,13 @@
         <v>319</v>
       </c>
       <c r="D30" t="n">
-        <v>96.05772723972439</v>
+        <v>319</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F30" t="n">
-        <v>319</v>
+        <v>96.05772723972458</v>
       </c>
       <c r="G30" t="n">
         <v>319</v>
@@ -29708,13 +29708,13 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -29903,7 +29903,7 @@
         <v>319</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,25 +29927,25 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>319</v>
+        <v>168.3712564811476</v>
       </c>
       <c r="T33" t="n">
         <v>319</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V33" t="n">
-        <v>286.0053395461672</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -30125,13 +30125,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>324.9501396486123</v>
@@ -30167,10 +30167,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
+        <v>124.2619859716246</v>
+      </c>
+      <c r="S36" t="n">
         <v>397</v>
-      </c>
-      <c r="S36" t="n">
-        <v>141.0873354980616</v>
       </c>
       <c r="T36" t="n">
         <v>397</v>
@@ -30182,7 +30182,7 @@
         <v>397</v>
       </c>
       <c r="W36" t="n">
-        <v>397</v>
+        <v>62.85180774469882</v>
       </c>
       <c r="X36" t="n">
         <v>397</v>
@@ -30201,19 +30201,19 @@
         <v>397</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>397</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>397</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>397</v>
       </c>
       <c r="F37" t="n">
         <v>397</v>
       </c>
       <c r="G37" t="n">
-        <v>244.3820695628415</v>
+        <v>397</v>
       </c>
       <c r="H37" t="n">
         <v>222.8870933147334</v>
@@ -30222,7 +30222,7 @@
         <v>156.7312261119215</v>
       </c>
       <c r="J37" t="n">
-        <v>54.03525007293729</v>
+        <v>149.2616797235074</v>
       </c>
       <c r="K37" t="n">
         <v>211.6312656044217</v>
@@ -30249,16 +30249,16 @@
         <v>397</v>
       </c>
       <c r="S37" t="n">
-        <v>397</v>
+        <v>350.8400534733473</v>
       </c>
       <c r="T37" t="n">
         <v>207.1968615882249</v>
       </c>
       <c r="U37" t="n">
-        <v>397</v>
+        <v>150.9222929138022</v>
       </c>
       <c r="V37" t="n">
-        <v>397</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
         <v>226.3728098387097</v>
@@ -30267,7 +30267,7 @@
         <v>397</v>
       </c>
       <c r="Y37" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="38">
@@ -30356,25 +30356,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9501396486123</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>252.6839047176626</v>
+        <v>140.4375005409272</v>
       </c>
       <c r="I39" t="n">
         <v>189.9476123064429</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
         <v>397</v>
@@ -30419,7 +30419,7 @@
         <v>397</v>
       </c>
       <c r="W39" t="n">
-        <v>397</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X39" t="n">
         <v>397</v>
@@ -30441,13 +30441,13 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>285.5362180555555</v>
+        <v>397</v>
       </c>
       <c r="E40" t="n">
-        <v>397</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>397</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
         <v>397</v>
@@ -30456,16 +30456,16 @@
         <v>397</v>
       </c>
       <c r="I40" t="n">
-        <v>397</v>
+        <v>310.3261490602512</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>397</v>
+        <v>211.6312656044217</v>
       </c>
       <c r="L40" t="n">
-        <v>369.8478840809211</v>
+        <v>325.1555297971234</v>
       </c>
       <c r="M40" t="n">
         <v>397</v>
@@ -30492,10 +30492,10 @@
         <v>207.1968615882249</v>
       </c>
       <c r="U40" t="n">
-        <v>150.9222929138022</v>
+        <v>397</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>397</v>
       </c>
       <c r="W40" t="n">
         <v>226.3728098387097</v>
@@ -30638,10 +30638,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>72.31352924142297</v>
+        <v>69.92675579599782</v>
       </c>
       <c r="R42" t="n">
-        <v>290.6132265545748</v>
+        <v>293</v>
       </c>
       <c r="S42" t="n">
         <v>293</v>
@@ -34743,19 +34743,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512562</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>242.0199542155221</v>
       </c>
       <c r="N2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>374</v>
@@ -34764,7 +34764,7 @@
         <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>242.0199542155222</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34880,7 +34880,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
@@ -34901,10 +34901,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>213.3459299699082</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>90.88798530595001</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34980,13 +34980,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L5" t="n">
-        <v>248.0502805878618</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
@@ -35001,7 +35001,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35126,19 +35126,19 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>8.285483532761353</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>173.5336330101307</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698063</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,16 +35220,16 @@
         <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>373.9999999999999</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
         <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
-        <v>235.5012052109774</v>
+        <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35357,28 +35357,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>51.00702550716294</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>40.68457074570025</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K11" t="n">
-        <v>187.673472361809</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L11" t="n">
-        <v>615.4736009529984</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M11" t="n">
-        <v>655.0000000000042</v>
+        <v>655</v>
       </c>
       <c r="N11" t="n">
-        <v>655.0000000000042</v>
+        <v>607.3433266784076</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K14" t="n">
-        <v>570.321535626366</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L14" t="n">
-        <v>232.8255376884423</v>
+        <v>655</v>
       </c>
       <c r="M14" t="n">
-        <v>655.0000000000038</v>
+        <v>655</v>
       </c>
       <c r="N14" t="n">
-        <v>655.0000000000038</v>
+        <v>185.1688643668502</v>
       </c>
       <c r="O14" t="n">
         <v>178.3365374610834</v>
@@ -35852,7 +35852,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K16" t="n">
-        <v>107.3687343955787</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35934,19 +35934,19 @@
         <v>187.673472361809</v>
       </c>
       <c r="L17" t="n">
-        <v>615.4736009529993</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M17" t="n">
-        <v>655.0000000000038</v>
+        <v>655</v>
       </c>
       <c r="N17" t="n">
-        <v>655.0000000000038</v>
+        <v>594.5220434248878</v>
       </c>
       <c r="O17" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P17" t="n">
-        <v>211.8739801603236</v>
+        <v>655</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -36089,7 +36089,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K19" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K20" t="n">
+        <v>187.6734723618091</v>
+      </c>
+      <c r="L20" t="n">
+        <v>232.8255376884422</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.989832208681229</v>
+      </c>
+      <c r="N20" t="n">
         <v>655</v>
-      </c>
-      <c r="L20" t="n">
-        <v>654.9999999999999</v>
-      </c>
-      <c r="M20" t="n">
-        <v>655.0000000000038</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
@@ -36186,7 +36186,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q20" t="n">
-        <v>148.1470733148123</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36326,7 +36326,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K22" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36408,13 +36408,13 @@
         <v>187.673472361809</v>
       </c>
       <c r="L23" t="n">
-        <v>615.4736009529979</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M23" t="n">
-        <v>655.0000000000044</v>
+        <v>435.2945687948379</v>
       </c>
       <c r="N23" t="n">
-        <v>655.0000000000044</v>
+        <v>655</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
@@ -36423,7 +36423,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36645,13 +36645,13 @@
         <v>187.673472361809</v>
       </c>
       <c r="L26" t="n">
-        <v>615.4736009530063</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M26" t="n">
-        <v>655.0000000000001</v>
+        <v>435.2945687948379</v>
       </c>
       <c r="N26" t="n">
-        <v>655.0000000000001</v>
+        <v>655</v>
       </c>
       <c r="O26" t="n">
         <v>178.3365374610834</v>
@@ -36660,7 +36660,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36800,7 +36800,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K28" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36888,7 +36888,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>372.8423367286592</v>
       </c>
       <c r="O29" t="n">
         <v>178.3365374610834</v>
@@ -36897,7 +36897,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q29" t="n">
-        <v>372.842336728659</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K31" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37076,7 +37076,7 @@
         <v>92.62719016129032</v>
       </c>
       <c r="X31" t="n">
-        <v>71.55635456989245</v>
+        <v>71.55635456989246</v>
       </c>
       <c r="Y31" t="n">
         <v>31.53464715053764</v>
@@ -37116,16 +37116,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K32" t="n">
-        <v>187.673472361809</v>
+        <v>655</v>
       </c>
       <c r="L32" t="n">
-        <v>615.4736009530058</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>655.0000000000006</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>655.0000000000006</v>
+        <v>200.7935788450894</v>
       </c>
       <c r="O32" t="n">
         <v>178.3365374610834</v>
@@ -37134,7 +37134,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37274,7 +37274,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K34" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37353,16 +37353,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K35" t="n">
-        <v>187.673472361809</v>
+        <v>374</v>
       </c>
       <c r="L35" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N35" t="n">
-        <v>374</v>
+        <v>19.67507097990872</v>
       </c>
       <c r="O35" t="n">
         <v>178.3365374610834</v>
@@ -37371,7 +37371,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q35" t="n">
-        <v>206.0015986180996</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37432,19 +37432,19 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K36" t="n">
-        <v>22.69379302306083</v>
+        <v>318.5740338860743</v>
       </c>
       <c r="L36" t="n">
-        <v>280.0644444388064</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>339.9353519954473</v>
+        <v>307.160421227325</v>
       </c>
       <c r="O36" t="n">
-        <v>374</v>
+        <v>46.59266649806909</v>
       </c>
       <c r="P36" t="n">
         <v>264.4060611184268</v>
@@ -37487,19 +37487,19 @@
         <v>109.8861996629213</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>124.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>111.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F37" t="n">
         <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>152.6179304371585</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>65.55579304030819</v>
+        <v>160.7822226908783</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -37535,16 +37535,16 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>46.15994652665276</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>246.0777070861978</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>197.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -37553,7 +37553,7 @@
         <v>149.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -37596,7 +37596,7 @@
         <v>232.8255376884423</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N38" t="n">
         <v>206.0015986180996</v>
@@ -37608,7 +37608,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q38" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,22 +37666,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K39" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L39" t="n">
-        <v>236.9437517198834</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M39" t="n">
-        <v>286.9650421645043</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O39" t="n">
-        <v>374</v>
+        <v>300.7827778944511</v>
       </c>
       <c r="P39" t="n">
         <v>264.4060611184268</v>
@@ -37727,13 +37727,13 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>111.4637819444445</v>
       </c>
       <c r="E40" t="n">
-        <v>116.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>122.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>152.6179304371585</v>
@@ -37742,16 +37742,16 @@
         <v>174.1129066852666</v>
       </c>
       <c r="I40" t="n">
-        <v>240.2687738880785</v>
+        <v>153.5949229483296</v>
       </c>
       <c r="J40" t="n">
         <v>11.52054296737091</v>
       </c>
       <c r="K40" t="n">
-        <v>185.3687343955783</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>44.69235428379768</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37778,10 +37778,10 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>246.0777070861978</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>197.8296897837838</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -37909,16 +37909,16 @@
         <v>318.5740338860743</v>
       </c>
       <c r="L42" t="n">
-        <v>324.1195555712401</v>
+        <v>311.5915370777239</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O42" t="n">
-        <v>374</v>
+        <v>46.59266649806909</v>
       </c>
       <c r="P42" t="n">
         <v>264.4060611184268</v>
@@ -37979,13 +37979,13 @@
         <v>70.11290668526664</v>
       </c>
       <c r="I43" t="n">
-        <v>136.2687738880785</v>
+        <v>136.2687738880784</v>
       </c>
       <c r="J43" t="n">
         <v>304.5205429673709</v>
       </c>
       <c r="K43" t="n">
-        <v>81.36873439557826</v>
+        <v>81.36873439557824</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>85.80313841177508</v>
+        <v>85.80313841177507</v>
       </c>
       <c r="U43" t="n">
         <v>142.0777070861978</v>
@@ -38073,16 +38073,16 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>374</v>
+        <v>43.87557877842326</v>
       </c>
       <c r="O44" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P44" t="n">
-        <v>211.8739801603236</v>
+        <v>374</v>
       </c>
       <c r="Q44" t="n">
-        <v>206.0015986180996</v>
+        <v>374</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38146,19 +38146,19 @@
         <v>318.5740338860743</v>
       </c>
       <c r="L45" t="n">
-        <v>364.5618469086669</v>
+        <v>374</v>
       </c>
       <c r="M45" t="n">
         <v>286.9650421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>209.7125587492164</v>
       </c>
       <c r="O45" t="n">
         <v>46.59266649806909</v>
       </c>
       <c r="P45" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
